--- a/public/templates/Radiography_Portable_Template.xlsx
+++ b/public/templates/Radiography_Portable_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS\anteso\anteso-frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A329912-839F-4AB0-A7BC-01E6CEA69DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB79BF-0D6A-4EE0-B160-02E838A0C9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1166,7 +1166,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M1 A13:M14 G11:H11 J11:M11 A4:M4 H3:M3 A6:E6 A5:B5 D5:M5 A8:M9 E7:M7 G6:M6 A2:H2 J2:M2 A10:F10 H10:M10 G12:M12 A17:M18 A15:E15 I15:M15 H16:M16 A21:M22 H20:M20 A19:H19 J19:M19 A29:M30 F28 J28 A27:C27 K27 L28:M28 A33:D33 L32:M32 G33:K33 M33 A31:F31 M27 A25:M26 H24 A23:F23 I23 J24:M24 K23:M23" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:M1 A13:M14 G11:H11 J11:M11 A4:M4 H3:M3 A6:E6 A5:B5 D5:M5 A8:M9 E7:M7 G6:M6 A2:H2 J2:M2 A10:F10 H10:M10 G12:M12 A17:M18 A15:E15 I15:M15 H16:M16 A22:M22 H20:M20 A19:H19 J19:M19 A29:M30 F28 J28 A27:C27 K27 L28:M28 A33:D33 L32:M32 G33:K33 M33 A31:F31 M27 A25:M26 H24 A23:F23 I23 J24:M24 K23:M23 A21:D21 F21:M21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
